--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H160"/>
+  <dimension ref="A1:H161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6778,6 +6778,46 @@
         <v>496.6</v>
       </c>
       <c r="H160" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>July_2026</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G161" t="n">
+        <v>243</v>
+      </c>
+      <c r="H161" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -6794,7 +6834,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H55"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8994,6 +9034,46 @@
         <v>22</v>
       </c>
       <c r="H55" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>July_2026</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Juan Cortes</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>WPS695</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>243</v>
+      </c>
+      <c r="H56" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H161"/>
+  <dimension ref="A1:H162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6818,6 +6818,46 @@
         <v>243</v>
       </c>
       <c r="H161" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>July_2026</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Miller Argarita</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>SMP854</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G162" t="n">
+        <v>415.1</v>
+      </c>
+      <c r="H162" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -9090,7 +9130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H76"/>
+  <dimension ref="A1:H77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12118,6 +12158,46 @@
         <v>496.6</v>
       </c>
       <c r="H76" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>July_2026</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Miller Argarita</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>SMP854</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>415.1</v>
+      </c>
+      <c r="H77" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H162"/>
+  <dimension ref="A1:H164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6858,6 +6858,86 @@
         <v>415.1</v>
       </c>
       <c r="H162" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>August_2026</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>miller</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>SUP857</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G163" t="n">
+        <v>1306.84</v>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>August_2026</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>miller</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>SUP857</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Toner</t>
+        </is>
+      </c>
+      <c r="G164" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H164" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -9130,7 +9210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H77"/>
+  <dimension ref="A1:H79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12198,6 +12278,86 @@
         <v>415.1</v>
       </c>
       <c r="H77" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>August_2026</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>miller</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>SUP857</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>1306.84</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>August_2026</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>miller</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>SUP857</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Toner</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H79" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H164"/>
+  <dimension ref="A1:H165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6938,6 +6938,46 @@
         <v>1.6</v>
       </c>
       <c r="H164" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>August_2026</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Nelson Tirado</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>TVY530</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G165" t="n">
+        <v>454.1</v>
+      </c>
+      <c r="H165" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -9210,7 +9250,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H79"/>
+  <dimension ref="A1:H80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12358,6 +12398,46 @@
         <v>1.6</v>
       </c>
       <c r="H79" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>August_2026</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Nelson Tirado</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>TVY530</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>454.1</v>
+      </c>
+      <c r="H80" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H165"/>
+  <dimension ref="A1:H167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6978,6 +6978,86 @@
         <v>454.1</v>
       </c>
       <c r="H165" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>August_2026</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Miller</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>SMP852</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G166" t="n">
+        <v>1470</v>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>August_2026</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Miller</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>SMP852</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G167" t="n">
+        <v>300</v>
+      </c>
+      <c r="H167" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -9250,7 +9330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H80"/>
+  <dimension ref="A1:H82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12438,6 +12518,86 @@
         <v>454.1</v>
       </c>
       <c r="H80" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>August_2026</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Miller</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>SMP852</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>1470</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>August_2026</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Miller</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>SMP852</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G82" t="n">
+        <v>300</v>
+      </c>
+      <c r="H82" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H167"/>
+  <dimension ref="A1:H168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7058,6 +7058,46 @@
         <v>300</v>
       </c>
       <c r="H167" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>August_2026</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Miller</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>WSP857</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Algodón</t>
+        </is>
+      </c>
+      <c r="G168" t="n">
+        <v>148.6</v>
+      </c>
+      <c r="H168" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -7074,7 +7114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H56"/>
+  <dimension ref="A1:H57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9314,6 +9354,46 @@
         <v>243</v>
       </c>
       <c r="H56" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>August_2026</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Miller</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>WSP857</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Algodón</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>148.6</v>
+      </c>
+      <c r="H57" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H168"/>
+  <dimension ref="A1:H169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7098,6 +7098,46 @@
         <v>148.6</v>
       </c>
       <c r="H168" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>August_2026</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Miller</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>WPS495</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G169" t="n">
+        <v>810.1</v>
+      </c>
+      <c r="H169" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -9410,7 +9450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H82"/>
+  <dimension ref="A1:H83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12678,6 +12718,46 @@
         <v>300</v>
       </c>
       <c r="H82" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>August_2026</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Miller</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>WPS495</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G83" t="n">
+        <v>810.1</v>
+      </c>
+      <c r="H83" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H169"/>
+  <dimension ref="A1:H170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7138,6 +7138,46 @@
         <v>810.1</v>
       </c>
       <c r="H169" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>September_2026</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Miller Arcila</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>SMP857</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G170" t="n">
+        <v>3310</v>
+      </c>
+      <c r="H170" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -7154,7 +7194,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H57"/>
+  <dimension ref="A1:H58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9434,6 +9474,46 @@
         <v>148.6</v>
       </c>
       <c r="H57" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>September_2026</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Miller Arcila</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>SMP857</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Retal de tela</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>3310</v>
+      </c>
+      <c r="H58" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H170"/>
+  <dimension ref="A1:H171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7178,6 +7178,46 @@
         <v>3310</v>
       </c>
       <c r="H170" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>September_2026</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Miller Arcila</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>SMP857</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G171" t="n">
+        <v>1447.2</v>
+      </c>
+      <c r="H171" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -9530,7 +9570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H83"/>
+  <dimension ref="A1:H84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12838,6 +12878,46 @@
         <v>810.1</v>
       </c>
       <c r="H83" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>September_2026</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Miller Arcila</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>SMP857</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G84" t="n">
+        <v>1447.2</v>
+      </c>
+      <c r="H84" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H171"/>
+  <dimension ref="A1:H173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7218,6 +7218,86 @@
         <v>1447.2</v>
       </c>
       <c r="H171" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>September_2026</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Miller Arcila</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>SMP897</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G172" t="n">
+        <v>191.2</v>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>September_2026</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Miller Arcila</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>SMP897</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Cortopunzante</t>
+        </is>
+      </c>
+      <c r="G173" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="H173" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -9570,7 +9650,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H84"/>
+  <dimension ref="A1:H86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12918,6 +12998,86 @@
         <v>1447.2</v>
       </c>
       <c r="H84" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>September_2026</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Miller Arcila</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>SMP897</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G85" t="n">
+        <v>191.2</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>September_2026</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Miller Arcila</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>SMP897</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Cortopunzante</t>
+        </is>
+      </c>
+      <c r="G86" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="H86" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H173"/>
+  <dimension ref="A1:H174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7298,6 +7298,46 @@
         <v>37.3</v>
       </c>
       <c r="H173" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>September_2026</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Miller Arcila</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>SMP857</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G174" t="n">
+        <v>171.1</v>
+      </c>
+      <c r="H174" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -9650,7 +9690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H86"/>
+  <dimension ref="A1:H87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13078,6 +13118,46 @@
         <v>37.3</v>
       </c>
       <c r="H86" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>September_2026</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Miller Arcila</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>SMP857</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G87" t="n">
+        <v>171.1</v>
+      </c>
+      <c r="H87" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H174"/>
+  <dimension ref="A1:H175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7338,6 +7338,46 @@
         <v>171.1</v>
       </c>
       <c r="H174" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>September_2026</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Jhon Cardona</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>NNL292</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Algodón</t>
+        </is>
+      </c>
+      <c r="G175" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="H175" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -7354,7 +7394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H58"/>
+  <dimension ref="A1:H59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9674,6 +9714,46 @@
         <v>3310</v>
       </c>
       <c r="H58" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>September_2026</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Jhon Cardona</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>NNL292</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Algodón</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="H59" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H175"/>
+  <dimension ref="A1:H176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7378,6 +7378,46 @@
         <v>63.3</v>
       </c>
       <c r="H175" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>September_2026</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Miller Arcila</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>SMP495</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G176" t="n">
+        <v>498.4</v>
+      </c>
+      <c r="H176" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -9770,7 +9810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H87"/>
+  <dimension ref="A1:H88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13238,6 +13278,46 @@
         <v>171.1</v>
       </c>
       <c r="H87" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>September_2026</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Miller Arcila</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>SMP495</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G88" t="n">
+        <v>498.4</v>
+      </c>
+      <c r="H88" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H176"/>
+  <dimension ref="A1:H177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7418,6 +7418,46 @@
         <v>498.4</v>
       </c>
       <c r="H176" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>September_2026</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Miller Arcila</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>SMP857</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G177" t="n">
+        <v>1500.3</v>
+      </c>
+      <c r="H177" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -7434,7 +7474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H59"/>
+  <dimension ref="A1:H60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9794,6 +9834,46 @@
         <v>63.3</v>
       </c>
       <c r="H59" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>September_2026</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Miller Arcila</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>SMP857</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>1500.3</v>
+      </c>
+      <c r="H60" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H177"/>
+  <dimension ref="A1:H178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7458,6 +7458,46 @@
         <v>1500.3</v>
       </c>
       <c r="H177" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>October_2026</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Miller Arcila</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>FVY530</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G178" t="n">
+        <v>324.3</v>
+      </c>
+      <c r="H178" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -9890,7 +9930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H88"/>
+  <dimension ref="A1:H89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13398,6 +13438,46 @@
         <v>498.4</v>
       </c>
       <c r="H88" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>October_2026</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Miller Arcila</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>FVY530</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G89" t="n">
+        <v>324.3</v>
+      </c>
+      <c r="H89" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H178"/>
+  <dimension ref="A1:H181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7498,6 +7498,126 @@
         <v>324.3</v>
       </c>
       <c r="H178" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>October_2026</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Jaime Serna</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>WLY707</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Aceite contaminado</t>
+        </is>
+      </c>
+      <c r="G179" t="n">
+        <v>750</v>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>October_2026</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Jaime Serna</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>WLY707</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G180" t="n">
+        <v>510.3</v>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>October_2026</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Jaime Serna</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>WLY707</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Vidrio</t>
+        </is>
+      </c>
+      <c r="G181" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="H181" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -9930,7 +10050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H89"/>
+  <dimension ref="A1:H92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13478,6 +13598,126 @@
         <v>324.3</v>
       </c>
       <c r="H89" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>October_2026</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Jaime Serna</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>WLY707</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Aceite contaminado</t>
+        </is>
+      </c>
+      <c r="G90" t="n">
+        <v>750</v>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>October_2026</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Jaime Serna</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>WLY707</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G91" t="n">
+        <v>510.3</v>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>October_2026</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Jaime Serna</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>WLY707</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Vidrio</t>
+        </is>
+      </c>
+      <c r="G92" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="H92" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H181"/>
+  <dimension ref="A1:H182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7618,6 +7618,46 @@
         <v>12.6</v>
       </c>
       <c r="H181" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>October_2026</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Norberto Jose Villadiego</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>NNM697</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G182" t="n">
+        <v>1317.4</v>
+      </c>
+      <c r="H182" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -7634,7 +7674,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H60"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10034,6 +10074,46 @@
         <v>1500.3</v>
       </c>
       <c r="H60" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>October_2026</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Norberto Jose Villadiego</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>NNM697</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>CDR</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>1317.4</v>
+      </c>
+      <c r="H61" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H182"/>
+  <dimension ref="A1:H183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7658,6 +7658,46 @@
         <v>1317.4</v>
       </c>
       <c r="H182" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>October_2026</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Jaime Serna</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>WLY707</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G183" t="n">
+        <v>970.6</v>
+      </c>
+      <c r="H183" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -10130,7 +10170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H92"/>
+  <dimension ref="A1:H93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13798,6 +13838,46 @@
         <v>12.6</v>
       </c>
       <c r="H92" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>October_2026</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Jaime Serna</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>WLY707</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G93" t="n">
+        <v>970.6</v>
+      </c>
+      <c r="H93" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H183"/>
+  <dimension ref="A1:H186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7698,6 +7698,126 @@
         <v>970.6</v>
       </c>
       <c r="H183" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>October_2026</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Jaime Serna</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>WLY707</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G184" t="n">
+        <v>551.3</v>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>October_2026</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Jaime Serna</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>WLY707</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Aceite</t>
+        </is>
+      </c>
+      <c r="G185" t="n">
+        <v>223.6</v>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>October_2026</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Jaime Serna</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>WLY707</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Cortopunzante</t>
+        </is>
+      </c>
+      <c r="G186" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="H186" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -10170,7 +10290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H93"/>
+  <dimension ref="A1:H96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13878,6 +13998,126 @@
         <v>970.6</v>
       </c>
       <c r="H93" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>October_2026</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Jaime Serna</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>WLY707</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G94" t="n">
+        <v>551.3</v>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>October_2026</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Jaime Serna</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>WLY707</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Aceite</t>
+        </is>
+      </c>
+      <c r="G95" t="n">
+        <v>223.6</v>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>October_2026</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Jaime Serna</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>WLY707</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Cortopunzante</t>
+        </is>
+      </c>
+      <c r="G96" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="H96" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H186"/>
+  <dimension ref="A1:H187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7818,6 +7818,46 @@
         <v>28.9</v>
       </c>
       <c r="H186" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>October_2026</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Jaime Serna</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>WLY707</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G187" t="n">
+        <v>227.9</v>
+      </c>
+      <c r="H187" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -10290,7 +10330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H96"/>
+  <dimension ref="A1:H97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14118,6 +14158,46 @@
         <v>28.9</v>
       </c>
       <c r="H96" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>October_2026</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Jaime Serna</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>WLY707</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G97" t="n">
+        <v>227.9</v>
+      </c>
+      <c r="H97" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H187"/>
+  <dimension ref="A1:H188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7858,6 +7858,46 @@
         <v>227.9</v>
       </c>
       <c r="H187" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>October_2026</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Sebastian Lopez</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>NNM697</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Algodón</t>
+        </is>
+      </c>
+      <c r="G188" t="n">
+        <v>68</v>
+      </c>
+      <c r="H188" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -7874,7 +7914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:H62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10314,6 +10354,46 @@
         <v>1317.4</v>
       </c>
       <c r="H61" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>October_2026</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>VEOLIA Aprovechables</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Sebastian Lopez</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>NNM697</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Algodón</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>68</v>
+      </c>
+      <c r="H62" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H188"/>
+  <dimension ref="A1:H190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7898,6 +7898,86 @@
         <v>68</v>
       </c>
       <c r="H188" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>October_2026</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Jaime Serna</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>WLY707</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G189" t="n">
+        <v>542.7</v>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>October_2026</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Jaime Serna</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>WLY707</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Aceites minerales y mezclas</t>
+        </is>
+      </c>
+      <c r="G190" t="n">
+        <v>156</v>
+      </c>
+      <c r="H190" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -10410,7 +10490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H97"/>
+  <dimension ref="A1:H99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14278,6 +14358,86 @@
         <v>227.9</v>
       </c>
       <c r="H97" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>October_2026</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Jaime Serna</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>WLY707</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G98" t="n">
+        <v>542.7</v>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>October_2026</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Jaime Serna</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>WLY707</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Aceites minerales y mezclas</t>
+        </is>
+      </c>
+      <c r="G99" t="n">
+        <v>156</v>
+      </c>
+      <c r="H99" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H190"/>
+  <dimension ref="A1:H191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7978,6 +7978,46 @@
         <v>156</v>
       </c>
       <c r="H190" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>October_2026</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Jaime Serna</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>WLY707</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G191" t="n">
+        <v>151.1</v>
+      </c>
+      <c r="H191" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
@@ -10490,7 +10530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H99"/>
+  <dimension ref="A1:H100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14438,6 +14478,46 @@
         <v>156</v>
       </c>
       <c r="H99" t="inlineStr">
+        <is>
+          <t>Sin novedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>October_2026</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>VEOLIA Peligrosos</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Jaime Serna</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>WLY707</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Solidos Contaminados</t>
+        </is>
+      </c>
+      <c r="G100" t="n">
+        <v>151.1</v>
+      </c>
+      <c r="H100" t="inlineStr">
         <is>
           <t>Sin novedades</t>
         </is>
